--- a/output/filter_review.xlsx
+++ b/output/filter_review.xlsx
@@ -353,43 +353,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>filter_name</t>
+          <t>rule_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>criterion_id</t>
+          <t>criterion_text</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>review_label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>criterion_text_category</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rule_type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source_workbook</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>join_operator</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>filter_criterion</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>value_count</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>review_label</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>explanation</t>
         </is>
       </c>
     </row>
@@ -401,15 +416,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>"Loan Date"."Loan Date" BETWEEN 2025-07-01 AND 2026-06-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>F1-C1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>"Loan Date"."Loan Date" BETWEEN 2025-07-01 AND 2026-06-30</t>
-        </is>
-      </c>
-      <c r="E2">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
     </row>
@@ -421,20 +446,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Lifecycle" = 'Active'</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>F2-C2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Lifecycle" = 'Active'</t>
-        </is>
-      </c>
-      <c r="E3">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
     </row>
@@ -446,20 +481,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>"Bibliographic Details"."Resource Type" IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>F2-C3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>"Bibliographic Details"."Resource Type" IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E4">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
@@ -471,20 +516,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>"Location"."Library Code (Active)" IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>F2-C4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>"Location"."Library Code (Active)" IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E5">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
@@ -496,20 +551,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>"Location"."Library Code" &lt;&gt; 'RES_SHARE'</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>F2-C5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>"Location"."Library Code" &lt;&gt; 'RES_SHARE'</t>
-        </is>
-      </c>
-      <c r="E6">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
@@ -521,20 +586,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>"Location"."Library Code" NOT LIKE '%equip%'</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>F2-C6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>"Location"."Library Code" NOT LIKE '%equip%'</t>
-        </is>
-      </c>
-      <c r="E7">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
@@ -546,20 +621,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>"Location"."Library Name" NOT LIKE '%equip%'</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>F2-C7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>"Location"."Library Name" NOT LIKE '%equip%'</t>
-        </is>
-      </c>
-      <c r="E8">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J8">
         <v>0</v>
       </c>
     </row>
@@ -571,20 +656,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'UNASSIGNED'</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>F2-C8</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'UNASSIGNED'</t>
-        </is>
-      </c>
-      <c r="E9">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J9">
         <v>0</v>
       </c>
     </row>
@@ -596,20 +691,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" NOT LIKE '%equip%'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>F2-C9</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" NOT LIKE '%equip%'</t>
-        </is>
-      </c>
-      <c r="E10">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J10">
         <v>0</v>
       </c>
     </row>
@@ -621,20 +726,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" NOT LIKE '%ithdraw%'</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>F2-C10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" NOT LIKE '%ithdraw%'</t>
-        </is>
-      </c>
-      <c r="E11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J11">
         <v>0</v>
       </c>
     </row>
@@ -646,20 +761,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" NOT LIKE '%equip%'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>F2-C11</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" NOT LIKE '%equip%'</t>
-        </is>
-      </c>
-      <c r="E12">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J12">
         <v>0</v>
       </c>
     </row>
@@ -671,20 +796,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Physical Item Id" NOT IN ('-1', '0')</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>F2-C12</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Physical Item Id" NOT IN ('-1', '0')</t>
-        </is>
-      </c>
-      <c r="E13">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J13">
         <v>0</v>
       </c>
     </row>
@@ -696,20 +831,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Item Policy" NOT LIKE '%equip%'</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>F2-C13</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Item Policy" NOT LIKE '%equip%'</t>
-        </is>
-      </c>
-      <c r="E14">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J14">
         <v>0</v>
       </c>
     </row>
@@ -721,20 +866,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>"Holdings Details"."Suppressed from Discovery" = 0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>F2-C14</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>"Holdings Details"."Suppressed from Discovery" = 0</t>
-        </is>
-      </c>
-      <c r="E15">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J15">
         <v>0</v>
       </c>
     </row>
@@ -746,20 +901,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>"Holdings Details"."Suppressed from Discovery by Suppressed Location" = 'No'</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>F2-C15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>"Holdings Details"."Suppressed from Discovery by Suppressed Location" = 'No'</t>
-        </is>
-      </c>
-      <c r="E16">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J16">
         <v>0</v>
       </c>
     </row>
@@ -771,20 +936,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>"Location"."Suppressed from Discovery" = 'No'</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>F2-C16</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>"Location"."Suppressed from Discovery" = 'No'</t>
-        </is>
-      </c>
-      <c r="E17">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J17">
         <v>0</v>
       </c>
     </row>
@@ -796,20 +971,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>"Bibliographic Details"."Suppressed From Discovery" = 'No'</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>F2-C17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>"Bibliographic Details"."Suppressed From Discovery" = 'No'</t>
-        </is>
-      </c>
-      <c r="E18">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J18">
         <v>0</v>
       </c>
     </row>
@@ -821,20 +1006,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Lifecycle" = 'Active'</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>F3-C18</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Lifecycle" = 'Active'</t>
-        </is>
-      </c>
-      <c r="E19">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J19">
         <v>0</v>
       </c>
     </row>
@@ -846,20 +1041,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN '$D 130 631' AND '$D 130 999'</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>F3-C19</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN '$D 130 631' AND '$D 130 999'</t>
-        </is>
-      </c>
-      <c r="E20">
+      <c r="J20">
         <v>0</v>
       </c>
     </row>
@@ -871,20 +1076,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN '$D 131 000' AND '$D 131 999'</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>F3-C20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN '$D 131 000' AND '$D 131 999'</t>
-        </is>
-      </c>
-      <c r="E21">
+      <c r="J21">
         <v>0</v>
       </c>
     </row>
@@ -896,20 +1111,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN '$D 132 000' AND '$D 132 991'</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>F3-C21</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN '$D 132 000' AND '$D 132 991'</t>
-        </is>
-      </c>
-      <c r="E22">
+      <c r="J22">
         <v>0</v>
       </c>
     </row>
@@ -921,20 +1146,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'A 2 539 991' AND 'A 2 540 384'</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>F3-C22</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'A 2 539 991' AND 'A 2 540 384'</t>
-        </is>
-      </c>
-      <c r="E23">
+      <c r="J23">
         <v>0</v>
       </c>
     </row>
@@ -946,20 +1181,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'CT 5 031 021' AND 'CT 5 044 752'</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>F3-C23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'CT 5 031 021' AND 'CT 5 044 752'</t>
-        </is>
-      </c>
-      <c r="E24">
+      <c r="J24">
         <v>0</v>
       </c>
     </row>
@@ -971,20 +1216,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'CT 5 045 001' AND 'CT 5 045 100'</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>F3-C24</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'CT 5 045 001' AND 'CT 5 045 100'</t>
-        </is>
-      </c>
-      <c r="E25">
+      <c r="J25">
         <v>0</v>
       </c>
     </row>
@@ -996,20 +1251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'D 2 648 821' AND 'D 2 650 043'</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>F3-C25</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'D 2 648 821' AND 'D 2 650 043'</t>
-        </is>
-      </c>
-      <c r="E26">
+      <c r="J26">
         <v>0</v>
       </c>
     </row>
@@ -1021,20 +1286,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'GR 44' AND 'GR 46'</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>F3-C26</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'GR 44' AND 'GR 46'</t>
-        </is>
-      </c>
-      <c r="E27">
+      <c r="J27">
         <v>0</v>
       </c>
     </row>
@@ -1046,20 +1321,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'JR 129 185' AND 'JR 129 185'</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>F3-C27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'JR 129 185' AND 'JR 129 185'</t>
-        </is>
-      </c>
-      <c r="E28">
+      <c r="J28">
         <v>0</v>
       </c>
     </row>
@@ -1071,20 +1356,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'JS 89 829' AND 'JS 89 893'</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>F3-C28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'JS 89 829' AND 'JS 89 893'</t>
-        </is>
-      </c>
-      <c r="E29">
+      <c r="J29">
         <v>0</v>
       </c>
     </row>
@@ -1096,20 +1391,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'KR 4 241' AND 'KR 4 361'</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>F3-C29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'KR 4 241' AND 'KR 4 361'</t>
-        </is>
-      </c>
-      <c r="E30">
+      <c r="J30">
         <v>0</v>
       </c>
     </row>
@@ -1121,20 +1426,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'KR 8 367' AND 'KR 8 400'</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>F3-C30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'KR 8 367' AND 'KR 8 400'</t>
-        </is>
-      </c>
-      <c r="E31">
+      <c r="J31">
         <v>0</v>
       </c>
     </row>
@@ -1146,20 +1461,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 79 560' AND 'MR 79 999'</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>F3-C31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 79 560' AND 'MR 79 999'</t>
-        </is>
-      </c>
-      <c r="E32">
+      <c r="J32">
         <v>0</v>
       </c>
     </row>
@@ -1171,20 +1496,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 80 000' AND 'MR 80 999'</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>F3-C32</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 80 000' AND 'MR 80 999'</t>
-        </is>
-      </c>
-      <c r="E33">
+      <c r="J33">
         <v>0</v>
       </c>
     </row>
@@ -1196,20 +1531,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 81 000' AND 'MR 81 999'</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>F3-C33</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 81 000' AND 'MR 81 999'</t>
-        </is>
-      </c>
-      <c r="E34">
+      <c r="J34">
         <v>0</v>
       </c>
     </row>
@@ -1221,20 +1566,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 82 000' AND 'MR 82 999'</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>F3-C34</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 82 000' AND 'MR 82 999'</t>
-        </is>
-      </c>
-      <c r="E35">
+      <c r="J35">
         <v>0</v>
       </c>
     </row>
@@ -1246,20 +1601,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 83 000' AND 'MR 83 999'</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>F3-C35</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 83 000' AND 'MR 83 999'</t>
-        </is>
-      </c>
-      <c r="E36">
+      <c r="J36">
         <v>0</v>
       </c>
     </row>
@@ -1271,20 +1636,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 84 000' AND 'MR 84 665'</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>F3-C36</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'MR 84 000' AND 'MR 84 665'</t>
-        </is>
-      </c>
-      <c r="E37">
+      <c r="J37">
         <v>0</v>
       </c>
     </row>
@@ -1296,20 +1671,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 668' AND 'Q 669'</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>F3-C37</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 668' AND 'Q 669'</t>
-        </is>
-      </c>
-      <c r="E38">
+      <c r="J38">
         <v>0</v>
       </c>
     </row>
@@ -1321,20 +1706,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 670' AND 'Q 670'</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>F3-C38</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 670' AND 'Q 670'</t>
-        </is>
-      </c>
-      <c r="E39">
+      <c r="J39">
         <v>0</v>
       </c>
     </row>
@@ -1346,20 +1741,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 1 088' AND 'Q 1 095'</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>F3-C39</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 1 088' AND 'Q 1 095'</t>
-        </is>
-      </c>
-      <c r="E40">
+      <c r="J40">
         <v>0</v>
       </c>
     </row>
@@ -1371,20 +1776,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 1 098' AND 'Q 1 125'</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>F3-C40</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 1 098' AND 'Q 1 125'</t>
-        </is>
-      </c>
-      <c r="E41">
+      <c r="J41">
         <v>0</v>
       </c>
     </row>
@@ -1396,20 +1811,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 1 127' AND 'Q 1 127'</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>F3-C41</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Q 1 127' AND 'Q 1 127'</t>
-        </is>
-      </c>
-      <c r="E42">
+      <c r="J42">
         <v>0</v>
       </c>
     </row>
@@ -1421,20 +1846,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'RLF50225052' AND 'RLF50339951'</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>F3-C42</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'RLF50225052' AND 'RLF50339951'</t>
-        </is>
-      </c>
-      <c r="E43">
+      <c r="J43">
         <v>0</v>
       </c>
     </row>
@@ -1446,20 +1881,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'U 193' AND 'U 199'</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>F3-C43</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'U 193' AND 'U 199'</t>
-        </is>
-      </c>
-      <c r="E44">
+      <c r="J44">
         <v>0</v>
       </c>
     </row>
@@ -1471,20 +1916,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'U 200' AND 'U 209'</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>F3-C44</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'U 200' AND 'U 209'</t>
-        </is>
-      </c>
-      <c r="E45">
+      <c r="J45">
         <v>0</v>
       </c>
     </row>
@@ -1496,20 +1951,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'U 210' AND 'U 219'</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>F3-C45</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'U 210' AND 'U 219'</t>
-        </is>
-      </c>
-      <c r="E46">
+      <c r="J46">
         <v>0</v>
       </c>
     </row>
@@ -1521,20 +1986,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'U 220' AND 'U 229'</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>F3-C46</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'U 220' AND 'U 229'</t>
-        </is>
-      </c>
-      <c r="E47">
+      <c r="J47">
         <v>0</v>
       </c>
     </row>
@@ -1546,20 +2021,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'U 230' AND 'U 235'</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>F3-C47</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'U 230' AND 'U 235'</t>
-        </is>
-      </c>
-      <c r="E48">
+      <c r="J48">
         <v>0</v>
       </c>
     </row>
@@ -1571,20 +2056,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'V 23 086' AND 'V 23 350'</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>F3-C48</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'V 23 086' AND 'V 23 350'</t>
-        </is>
-      </c>
-      <c r="E49">
+      <c r="J49">
         <v>0</v>
       </c>
     </row>
@@ -1596,20 +2091,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'W 337 560' AND 'W 337 999'</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>F3-C49</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'W 337 560' AND 'W 337 999'</t>
-        </is>
-      </c>
-      <c r="E50">
+      <c r="J50">
         <v>0</v>
       </c>
     </row>
@@ -1621,20 +2126,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'W 338 000' AND 'W 338 999'</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>F3-C50</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'W 338 000' AND 'W 338 999'</t>
-        </is>
-      </c>
-      <c r="E51">
+      <c r="J51">
         <v>0</v>
       </c>
     </row>
@@ -1646,20 +2161,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'W 339 000' AND 'W 339 999'</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>F3-C51</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'W 339 000' AND 'W 339 999'</t>
-        </is>
-      </c>
-      <c r="E52">
+      <c r="J52">
         <v>0</v>
       </c>
     </row>
@@ -1671,20 +2196,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'W 340 000' AND 'W 340 999'</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>F3-C52</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'W 340 000' AND 'W 340 999'</t>
-        </is>
-      </c>
-      <c r="E53">
+      <c r="J53">
         <v>0</v>
       </c>
     </row>
@@ -1696,20 +2231,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'W 341 000' AND 'W 341 999'</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>F3-C53</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'W 341 000' AND 'W 341 999'</t>
-        </is>
-      </c>
-      <c r="E54">
+      <c r="J54">
         <v>0</v>
       </c>
     </row>
@@ -1721,20 +2266,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'W 342 000' AND 'W 342 723'</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>F3-C54</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'W 342 000' AND 'W 342 723'</t>
-        </is>
-      </c>
-      <c r="E55">
+      <c r="J55">
         <v>0</v>
       </c>
     </row>
@@ -1746,20 +2301,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'WC 34 094' AND 'WC 34 999'</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>F3-C55</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'WC 34 094' AND 'WC 34 999'</t>
-        </is>
-      </c>
-      <c r="E56">
+      <c r="J56">
         <v>0</v>
       </c>
     </row>
@@ -1771,20 +2336,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'WC 35 000' AND 'WC 35 067'</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>F3-C56</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'WC 35 000' AND 'WC 35 067'</t>
-        </is>
-      </c>
-      <c r="E57">
+      <c r="J57">
         <v>0</v>
       </c>
     </row>
@@ -1796,20 +2371,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'X 97 126' AND 'X 97 999'</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>F3-C57</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'X 97 126' AND 'X 97 999'</t>
-        </is>
-      </c>
-      <c r="E58">
+      <c r="J58">
         <v>0</v>
       </c>
     </row>
@@ -1821,20 +2406,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'X 98 000' AND 'X 98 480'</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>F3-C58</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'X 98 000' AND 'X 98 480'</t>
-        </is>
-      </c>
-      <c r="E59">
+      <c r="J59">
         <v>0</v>
       </c>
     </row>
@@ -1846,20 +2441,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Y 13 844' AND 'Y 13 930'</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>F3-C59</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Y 13 844' AND 'Y 13 930'</t>
-        </is>
-      </c>
-      <c r="E60">
+      <c r="J60">
         <v>0</v>
       </c>
     </row>
@@ -1871,20 +2476,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 18 811' AND 'Z 18 996'</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>F3-C60</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 18 811' AND 'Z 18 996'</t>
-        </is>
-      </c>
-      <c r="E61">
+      <c r="J61">
         <v>0</v>
       </c>
     </row>
@@ -1896,20 +2511,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 18 998' AND 'Z 18 999'</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>F3-C61</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 18 998' AND 'Z 18 999'</t>
-        </is>
-      </c>
-      <c r="E62">
+      <c r="J62">
         <v>0</v>
       </c>
     </row>
@@ -1921,20 +2546,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 19 000' AND 'Z 19 024'</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>F3-C62</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 19 000' AND 'Z 19 024'</t>
-        </is>
-      </c>
-      <c r="E63">
+      <c r="J63">
         <v>0</v>
       </c>
     </row>
@@ -1946,20 +2581,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 19 027' AND 'Z 19 027'</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>F3-C63</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" BETWEEN 'Z 19 027' AND 'Z 19 027'</t>
-        </is>
-      </c>
-      <c r="E64">
+      <c r="J64">
         <v>0</v>
       </c>
     </row>
@@ -1971,20 +2616,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN ('Z 18 798', 'Z 18 799')</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>F3-C64</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN ('Z 18 798', 'Z 18 799')</t>
-        </is>
-      </c>
-      <c r="E65">
+      <c r="J65">
         <v>2</v>
       </c>
     </row>
@@ -1996,20 +2651,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Lifecycle" = 'Active'</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>F4-C65</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Lifecycle" = 'Active'</t>
-        </is>
-      </c>
-      <c r="E66">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J66">
         <v>0</v>
       </c>
     </row>
@@ -2021,20 +2686,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>F4-C66</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E67">
+      <c r="J67">
         <v>9999</v>
       </c>
     </row>
@@ -2046,20 +2721,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>F4-C67</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E68">
+      <c r="J68">
         <v>9999</v>
       </c>
     </row>
@@ -2071,20 +2756,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>F4-C68</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E69">
+      <c r="J69">
         <v>9999</v>
       </c>
     </row>
@@ -2096,20 +2791,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>F4-C69</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E70">
+      <c r="J70">
         <v>9999</v>
       </c>
     </row>
@@ -2121,20 +2826,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>F4-C70</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E71">
+      <c r="J71">
         <v>9999</v>
       </c>
     </row>
@@ -2146,20 +2861,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>F4-C71</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E72">
+      <c r="J72">
         <v>9999</v>
       </c>
     </row>
@@ -2171,20 +2896,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>F4-C72</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (9,999 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E73">
+      <c r="J73">
         <v>9999</v>
       </c>
     </row>
@@ -2196,20 +2931,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Barcode" IN (5,281 values; see Value List Summary and companion CSV)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>F4-C73</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Barcode" IN (5,281 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E74">
+      <c r="J74">
         <v>5281</v>
       </c>
     </row>
@@ -2221,20 +2966,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'lis'</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>F5-C74</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'lis'</t>
-        </is>
-      </c>
-      <c r="E75">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J75">
         <v>0</v>
       </c>
     </row>
@@ -2246,20 +3001,30 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'nzw'</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>F5-C75</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'nzw'</t>
-        </is>
-      </c>
-      <c r="E76">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J76">
         <v>0</v>
       </c>
     </row>
@@ -2271,20 +3036,30 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'zwz'</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>F5-C76</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'zwz'</t>
-        </is>
-      </c>
-      <c r="E77">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J77">
         <v>0</v>
       </c>
     </row>
@@ -2296,20 +3071,30 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" NOT LIKE '%zw%'</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>F5-C77</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" NOT LIKE '%zw%'</t>
-        </is>
-      </c>
-      <c r="E78">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J78">
         <v>0</v>
       </c>
     </row>
@@ -2321,20 +3106,30 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" NOT LIKE '%ithdraw%'</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>F5-C78</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" NOT LIKE '%ithdraw%'</t>
-        </is>
-      </c>
-      <c r="E79">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J79">
         <v>0</v>
       </c>
     </row>
@@ -2346,20 +3141,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" NOT LIKE '%ITHDRAW%'</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>F5-C79</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" NOT LIKE '%ITHDRAW%'</t>
-        </is>
-      </c>
-      <c r="E80">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J80">
         <v>0</v>
       </c>
     </row>
@@ -2371,20 +3176,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" IS NULL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>F5-C80</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" IS NULL</t>
-        </is>
-      </c>
-      <c r="E81">
+      <c r="J81">
         <v>0</v>
       </c>
     </row>
@@ -2396,20 +3211,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>F5-C81</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E82">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J82">
         <v>0</v>
       </c>
     </row>
@@ -2421,20 +3246,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" NOT LIKE 'wds%'</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>F5-C82</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" NOT LIKE 'wds%'</t>
-        </is>
-      </c>
-      <c r="E83">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J83">
         <v>0</v>
       </c>
     </row>
@@ -2446,20 +3281,30 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" NOT LIKE 'wms%'</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>F5-C83</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" NOT LIKE 'wms%'</t>
-        </is>
-      </c>
-      <c r="E84">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J84">
         <v>0</v>
       </c>
     </row>
@@ -2471,20 +3316,30 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" NOT LIKE 'wor%'</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>F5-C84</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" NOT LIKE 'wor%'</t>
-        </is>
-      </c>
-      <c r="E85">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J85">
         <v>0</v>
       </c>
     </row>
@@ -2496,20 +3351,30 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>NOT (DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6532 AND "Location"."Library Code" = 'BANC' AND "Physical Item Details"."Item Policy" IN ('Other Archival Material', 'Personal Manuscript', 'UC Archival Manuscript', 'Visual Material: pictorial'))</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>F6-C85</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NOT (DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6532 AND "Location"."Library Code" = 'BANC' AND "Physical Item Details"."Item Policy" IN ('Other Archival Material', 'Personal Manuscript', 'UC Archival Manuscript', 'Visual Material: pictorial'))</t>
-        </is>
-      </c>
-      <c r="E86">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J86">
         <v>0</v>
       </c>
     </row>
@@ -2521,20 +3386,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>NOT (DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6532 AND "Location"."Library Code" = 'NRLF' AND "Location"."Location Code" IN ('nbtbr', 'nbtur') AND "Physical Item Details"."Item Policy" IN ('Other Archival Material', 'Personal Manuscript', 'UC Archival Manuscript', 'Visual Material: pictorial'))</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>F6-C86</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NOT (DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6532 AND "Location"."Library Code" = 'NRLF' AND "Location"."Location Code" IN ('nbtbr', 'nbtur') AND "Physical Item Details"."Item Policy" IN ('Other Archival Material', 'Personal Manuscript', 'UC Archival Manuscript', 'Visual Material: pictorial'))</t>
-        </is>
-      </c>
-      <c r="E87">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J87">
         <v>0</v>
       </c>
     </row>
@@ -2546,20 +3421,30 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 3126 AND "Location"."Library Code" = ('NRLF'))</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>F7-C87</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 3126 AND "Location"."Library Code" = ('NRLF'))</t>
-        </is>
-      </c>
-      <c r="E88">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J88">
         <v>0</v>
       </c>
     </row>
@@ -2571,20 +3456,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 3126 AND "Location"."Library Code" = ('SRLF'))</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>F7-C88</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 3126 AND "Location"."Library Code" = ('SRLF'))</t>
-        </is>
-      </c>
-      <c r="E89">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J89">
         <v>0</v>
       </c>
     </row>
@@ -2596,20 +3491,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 3126 AND "Location"."Location Code" = ('NRLF'))</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>F7-C89</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 3126 AND "Location"."Location Code" = ('NRLF'))</t>
-        </is>
-      </c>
-      <c r="E90">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J90">
         <v>0</v>
       </c>
     </row>
@@ -2621,20 +3526,30 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" NOT IN ('gmlml', 'gmlill', 'xlle', 'xllck', 'xllhk', 'xmllk', 'nrlf', 'srlfm', 'srlf', 'srlfr', 'llill_rsl', 'lawill_rsl', 'slill')</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>F8-C90</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" NOT IN (13 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E91">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J91">
         <v>13</v>
       </c>
     </row>
@@ -2646,20 +3561,30 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" NOT IN ('zz', 'Problem location from Migration')</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>F8-C91</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" NOT IN ('zz', 'Problem location from Migration')</t>
-        </is>
-      </c>
-      <c r="E92">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J92">
         <v>2</v>
       </c>
     </row>
@@ -2671,20 +3596,30 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>"Library Unit"."Library Code" NOT IN ('AYALA', 'OCSEAA')</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>F8-C92</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>"Library Unit"."Library Code" NOT IN ('AYALA', 'OCSEAA')</t>
-        </is>
-      </c>
-      <c r="E93">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J93">
         <v>2</v>
       </c>
     </row>
@@ -2696,20 +3631,30 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>"Location"."Library Name" NOT IN ('X_Do_Not_Use_Old_Orange County &amp; Southeast Asian Archive Center', 'X_Do_Not_Use_Old_Science Library')</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>F8-C93</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>"Location"."Library Name" NOT IN ('X_Do_Not_Use_Old_Orange County &amp; Southeast Asian Archive Center', 'X_Do_Not_Use_Old_Science Library')</t>
-        </is>
-      </c>
-      <c r="E94">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J94">
         <v>2</v>
       </c>
     </row>
@@ -2721,20 +3666,30 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" IS NULL</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>F8-C94</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" IS NULL</t>
-        </is>
-      </c>
-      <c r="E95">
+      <c r="J95">
         <v>0</v>
       </c>
     </row>
@@ -2746,20 +3701,30 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>F8-C95</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E96">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J96">
         <v>0</v>
       </c>
     </row>
@@ -2771,20 +3736,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" = '-')</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>F8-C96</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" = '-')</t>
-        </is>
-      </c>
-      <c r="E97">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J97">
         <v>0</v>
       </c>
     </row>
@@ -2796,20 +3771,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE 'from%')</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>F8-C97</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE 'from%')</t>
-        </is>
-      </c>
-      <c r="E98">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J98">
         <v>0</v>
       </c>
     </row>
@@ -2821,20 +3806,30 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%rlf-%')</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>F8-C98</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%rlf-%')</t>
-        </is>
-      </c>
-      <c r="E99">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J99">
         <v>0</v>
       </c>
     </row>
@@ -2846,20 +3841,30 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%sp-%')</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>F8-C99</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%sp-%')</t>
-        </is>
-      </c>
-      <c r="E100">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J100">
         <v>0</v>
       </c>
     </row>
@@ -2871,20 +3876,30 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%wd%')</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>F8-C100</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%wd%')</t>
-        </is>
-      </c>
-      <c r="E101">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J101">
         <v>0</v>
       </c>
     </row>
@@ -2896,20 +3911,30 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%ithd%')</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>F8-C101</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" LIKE '%ithd%')</t>
-        </is>
-      </c>
-      <c r="E102">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J102">
         <v>0</v>
       </c>
     </row>
@@ -2921,20 +3946,30 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>"Bibliographic Details"."Uniform Resource Identifier" IS NULL</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>F9-C102</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>"Bibliographic Details"."Uniform Resource Identifier" IS NULL</t>
-        </is>
-      </c>
-      <c r="E103">
+      <c r="J103">
         <v>0</v>
       </c>
     </row>
@@ -2946,20 +3981,30 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>"Bibliographic Details"."Uniform Resource Identifier" IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>F9-C103</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>"Bibliographic Details"."Uniform Resource Identifier" IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E104">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J104">
         <v>0</v>
       </c>
     </row>
@@ -2971,20 +4016,30 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%findaid%'))</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>F9-C104</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%findaid%'))</t>
-        </is>
-      </c>
-      <c r="E105">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J105">
         <v>0</v>
       </c>
     </row>
@@ -2996,20 +4051,30 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%oac.cdlib%'))</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>F9-C105</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%oac.cdlib%'))</t>
-        </is>
-      </c>
-      <c r="E106">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J106">
         <v>0</v>
       </c>
     </row>
@@ -3021,20 +4086,30 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" &lt;&gt; 'Problem location from Migration'</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>F10-C106</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" &lt;&gt; 'Problem location from Migration'</t>
-        </is>
-      </c>
-      <c r="E107">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J107">
         <v>0</v>
       </c>
     </row>
@@ -3046,20 +4121,30 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>"Library Unit"."Library Code" NOT IN ('CLICC', 'CLICC_LOCKER', 'CLEANUP')</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t>F10-C107</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>"Library Unit"."Library Code" NOT IN ('CLICC', 'CLICC_LOCKER', 'CLEANUP')</t>
-        </is>
-      </c>
-      <c r="E108">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J108">
         <v>3</v>
       </c>
     </row>
@@ -3071,20 +4156,30 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6533 AND "Physical Item Details"."Item Policy" LIKE '%CLICC%')</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>F10-C108</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6533 AND "Physical Item Details"."Item Policy" LIKE '%CLICC%')</t>
-        </is>
-      </c>
-      <c r="E109">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J109">
         <v>0</v>
       </c>
     </row>
@@ -3096,20 +4191,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6533 AND "Physical Item Details"."Item Policy" LIKE '%hrome%ook%')</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>F10-C109</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6533 AND "Physical Item Details"."Item Policy" LIKE '%hrome%ook%')</t>
-        </is>
-      </c>
-      <c r="E110">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J110">
         <v>0</v>
       </c>
     </row>
@@ -3121,15 +4226,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6533 AND "Bibliographic Details"."Material Type" = 'Mixed material')</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>F11-C110</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 6533 AND "Bibliographic Details"."Material Type" = 'Mixed material')</t>
-        </is>
-      </c>
-      <c r="E111">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="J111">
         <v>0</v>
       </c>
     </row>
@@ -3141,20 +4256,30 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'srlf'</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>F12-C111</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'srlf'</t>
-        </is>
-      </c>
-      <c r="E112">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J112">
         <v>0</v>
       </c>
     </row>
@@ -3166,20 +4291,30 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'xxx'</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>F12-C112</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'xxx'</t>
-        </is>
-      </c>
-      <c r="E113">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J113">
         <v>0</v>
       </c>
     </row>
@@ -3191,20 +4326,30 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" NOT IN ('zzCleanmxus', 'zzCleanedr', 'zzCleangf', 'zzCleango', 'zzCleangous', 'zzCleangpin', 'zzCleanr', 'zzCleanrccd', 'zzCleanrcp', 'zzCleanrroom', 'zzCleans', 'zzCleansccd', 'zzCleanscirs', 'zzCleansroom', 'zzCleanv', 'zzCleanvcas', 'zzCleanvcirc', 'zzDelete', 'Problem location from Migration')</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>F12-C113</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" NOT IN (19 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E114">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J114">
         <v>19</v>
       </c>
     </row>
@@ -3216,15 +4361,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4706 AND "Location"."Location Name" IN ('Southern Regional Library Facility Special Collections &amp; University Archives', 'Special Collections', 'Special Collections Archives', 'Special Collections Artists Books', 'Special Collections Artists Books Flat', 'Special Collections Artists Books Oversize', 'Special Collections Artists Books Tiny', 'Special Collections Artists Books Vault', 'Special Collections CD', 'Special Collections Computer File', 'Special Collections Costo', 'Special Collections Costo Oversize', 'Special Collections Costo Oversize V', 'Special Collections Costo Vault', 'Special Collections Flat', 'Special Collections Flat V', 'Special Collections Leaves Flat Vault', 'Special Collections Leaves Oversize Vault', 'Special Collections Leaves Tiny Vault', 'Special Collections Leaves Vault', 'Special Collections Manuscripts', 'Special Collections Map Case', 'Special Collections Map Rivera', 'Special Collections Oversize', 'Special Collections Oversize Vault', 'Special Collections Pamphlets', 'Special Collections Photo', 'Special Collections Photo Oversize', 'Special Collections Reserve', 'Special Collections Staff Reference', 'Special Collections Thesis', 'Special Collections Tiny', 'Special Collections Tiny Vault', 'Special Collections Traven', 'Special Collections Traven Oversize', 'Special Collections Traven Vault', 'Special Collections Vault', 'Special Collections Video Tape') AND "Physical Item Details"."Material Type" = 'Archival Material')</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>F13-C114</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4706 AND "Location"."Location Name" IN ('Southern Regional Library Facility Special Collections &amp; University Archives', 'Special Collections', 'Special Collections Archives', 'Special Collections Artists Books', 'Special Collections Artists Books Flat', 'Special Collections Artists Books Oversize', 'Special Collections Artists Books Tiny', 'Special Collections Artists Books Vault', 'Special Collections CD', 'Special Collections Computer File', 'Special Collections Costo', 'Special Collections Costo Oversize', 'Special Collections Costo Oversize V', 'Special Collections Costo Vault', 'Special Collections Flat', 'Special Collections Flat V', 'Special Collections Leaves Flat Vault', 'Special Collections Leaves Oversize Vault', 'Special Collections Leaves Tiny Vault', 'Special Collections Leaves Vault', 'Special Collections Manuscripts', 'Special Collections Map Case', 'Special Collections Map Rivera', 'Special Collections Oversize', 'Special Collections Oversize Vault', 'Special Collections Pamphlets', 'Special Collections Photo', 'Special Collections Photo Oversize', 'Special Collections Reserve', 'Special Collections Staff Reference', 'Special Collections Thesis', 'Special Collections Tiny', 'Special Collections Tiny Vault', 'Special Collections Traven', 'Special Collections Traven Oversize', 'Special Collections Traven Vault', 'Special Collections Vault', 'Special Collections Video Tape') AND "Physical Item Details"."Material Type" = 'Archival Material')</t>
-        </is>
-      </c>
-      <c r="E115">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="J115">
         <v>0</v>
       </c>
     </row>
@@ -3236,15 +4391,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'srlf'</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t>F14-C115</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'srlf'</t>
-        </is>
-      </c>
-      <c r="E116">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="J116">
         <v>0</v>
       </c>
     </row>
@@ -3256,20 +4421,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" NOT IN ('srlf', 'zdelete', 'zdelete15', 'SRLF', 'spnr')</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t>F15-C116</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" NOT IN ('srlf', 'zdelete', 'zdelete15', 'SRLF', 'spnr')</t>
-        </is>
-      </c>
-      <c r="E117">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J117">
         <v>5</v>
       </c>
     </row>
@@ -3281,20 +4456,30 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" &lt;&gt; 'zdelete'</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>F15-C117</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" &lt;&gt; 'zdelete'</t>
-        </is>
-      </c>
-      <c r="E118">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J118">
         <v>0</v>
       </c>
     </row>
@@ -3306,20 +4491,30 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>NOT("Location"."Location Code" IN ('spc', 'spann', 'spanv', 'sprice', 'spred', 'spwhi', 'spflm', 'spnr', 'spovr', 'spovm') AND "Holding Details"."Permanent Call Number" LIKE 'UA%')</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>F16-C118</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>NOT("Location"."Location Code" IN ('spc', 'spann', 'spanv', 'sprice', 'spred', 'spwhi', 'spflm', 'spnr', 'spovr', 'spovm') AND "Holding Details"."Permanent Call Number" LIKE 'UA%')</t>
-        </is>
-      </c>
-      <c r="E119">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J119">
         <v>0</v>
       </c>
     </row>
@@ -3331,20 +4526,30 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>NOT("Location"."Location Code" IN ('spc', 'spann', 'spanv', 'sprice', 'spred', 'spwhi', 'spflm', 'spnr', 'spovr', 'spovm') AND "Holding Details"."Permanent Call Number" LIKE 'MS%')</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>F16-C119</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>NOT("Location"."Location Code" IN ('spc', 'spann', 'spanv', 'sprice', 'spred', 'spwhi', 'spflm', 'spnr', 'spovr', 'spovm') AND "Holding Details"."Permanent Call Number" LIKE 'MS%')</t>
-        </is>
-      </c>
-      <c r="E120">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J120">
         <v>0</v>
       </c>
     </row>
@@ -3356,20 +4561,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" NOT IN ('cc_borbot', 'cc_flr2', 'cc_stor', 'desk', 'srlf', 'SRLF')</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>F17-C120</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" NOT IN ('cc_borbot', 'cc_flr2', 'cc_stor', 'desk', 'srlf', 'SRLF')</t>
-        </is>
-      </c>
-      <c r="E121">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J121">
         <v>0</v>
       </c>
     </row>
@@ -3381,20 +4596,30 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" &lt;&gt; 'Problem location from Migration'</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>F17-C121</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" &lt;&gt; 'Problem location from Migration'</t>
-        </is>
-      </c>
-      <c r="E122">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J122">
         <v>0</v>
       </c>
     </row>
@@ -3406,20 +4631,30 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'SAC%')</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>F18-C122</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'SAC%')</t>
-        </is>
-      </c>
-      <c r="E123">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J123">
         <v>0</v>
       </c>
     </row>
@@ -3431,20 +4666,30 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
+          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'SMC%')</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>F18-C123</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'SMC%')</t>
-        </is>
-      </c>
-      <c r="E124">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J124">
         <v>0</v>
       </c>
     </row>
@@ -3456,20 +4701,30 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
+          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'MSS%')</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t>F18-C124</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'MSS%')</t>
-        </is>
-      </c>
-      <c r="E125">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J125">
         <v>0</v>
       </c>
     </row>
@@ -3481,20 +4736,30 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'RSS%')</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t>F18-C125</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>NOT("Location"."Library Code" IN ('SCA') AND "Holding Details"."Permanent Call Number" LIKE 'RSS%')</t>
-        </is>
-      </c>
-      <c r="E126">
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J126">
         <v>0</v>
       </c>
     </row>
@@ -3506,15 +4771,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" &lt;&gt; 'frsno'</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t>F19-C126</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" &lt;&gt; 'frsno'</t>
-        </is>
-      </c>
-      <c r="E127">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="J127">
         <v>0</v>
       </c>
     </row>
@@ -3526,20 +4801,30 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
+          <t>"Location"."Location Code" NOT IN ('gmlml', 'gmlill', 'xlle', 'xllck', 'xllhk', 'xmllk', 'nrlf', 'srlfm', 'srlf', 'srlfr', 'llill_rsl', 'lawill_rsl', 'slill')</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>F20-C127</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>"Location"."Location Code" NOT IN (13 values; see Value List Summary and companion CSV)</t>
-        </is>
-      </c>
-      <c r="E128">
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J128">
         <v>13</v>
       </c>
     </row>
@@ -3551,20 +4836,30 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>"Location"."Location Name" NOT IN ('zz', 'Problem location from Migration')</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t>F20-C128</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>"Location"."Location Name" NOT IN ('zz', 'Problem location from Migration')</t>
-        </is>
-      </c>
-      <c r="E129">
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J129">
         <v>2</v>
       </c>
     </row>
@@ -3576,20 +4871,30 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
+          <t>"Library Unit"."Library Code" NOT IN ('AYALA', 'OCSEAA')</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>F20-C129</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>"Library Unit"."Library Code" NOT IN ('AYALA', 'OCSEAA')</t>
-        </is>
-      </c>
-      <c r="E130">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J130">
         <v>2</v>
       </c>
     </row>
@@ -3601,20 +4906,30 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
+          <t>"Location"."Library Name" NOT IN ('X_Do_Not_Use_Old_Orange County &amp; Southeast Asian Archive Center', 'X_Do_Not_Use_Old_Science Library')</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>F20-C130</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>"Location"."Library Name" NOT IN ('X_Do_Not_Use_Old_Orange County &amp; Southeast Asian Archive Center', 'X_Do_Not_Use_Old_Science Library')</t>
-        </is>
-      </c>
-      <c r="E131">
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J131">
         <v>2</v>
       </c>
     </row>
@@ -3626,20 +4941,30 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" IS NULL</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>F20-C131</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" IS NULL</t>
-        </is>
-      </c>
-      <c r="E132">
+      <c r="J132">
         <v>0</v>
       </c>
     </row>
@@ -3651,20 +4976,30 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t>"Physical Item Details"."Statistics Note 2" IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>F20-C132</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>"Physical Item Details"."Statistics Note 2" IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E133">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J133">
         <v>0</v>
       </c>
     </row>
@@ -3676,20 +5011,30 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
+          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" &lt;&gt; '-'</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>F20-C133</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" &lt;&gt; '-'</t>
-        </is>
-      </c>
-      <c r="E134">
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J134">
         <v>0</v>
       </c>
     </row>
@@ -3701,20 +5046,30 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE 'from%'</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>F20-C134</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE 'from%'</t>
-        </is>
-      </c>
-      <c r="E135">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J135">
         <v>0</v>
       </c>
     </row>
@@ -3726,20 +5081,30 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
+          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%rlf-%'</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t>F20-C135</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%rlf-%'</t>
-        </is>
-      </c>
-      <c r="E136">
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J136">
         <v>0</v>
       </c>
     </row>
@@ -3751,20 +5116,30 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%sp-%'</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t>F20-C136</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%sp-%'</t>
-        </is>
-      </c>
-      <c r="E137">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J137">
         <v>0</v>
       </c>
     </row>
@@ -3776,20 +5151,30 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%wd%'</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
           <t>F20-C137</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%wd%'</t>
-        </is>
-      </c>
-      <c r="E138">
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J138">
         <v>0</v>
       </c>
     </row>
@@ -3801,20 +5186,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%ithd%'</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t>F20-C138</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Physical Item Details"."Statistics Note 2" NOT LIKE '%ithd%'</t>
-        </is>
-      </c>
-      <c r="E139">
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J139">
         <v>0</v>
       </c>
     </row>
@@ -3826,20 +5221,30 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%findaid%'))</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>F21-C139</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%findaid%'))</t>
-        </is>
-      </c>
-      <c r="E140">
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J140">
         <v>0</v>
       </c>
     </row>
@@ -3851,20 +5256,30 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
+          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%oac.cdlib%'))</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t>F21-C140</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>NOT(DESCRIPTOR_IDOF("Physical Items"."Institution"."Institution Name") = 4701 AND "Location"."Location Code" IN ('gocrh', 'gseaa', 'spcol') AND ("Bibliographic Details"."Uniform Resource Identifier" LIKE '%oac.cdlib%'))</t>
-        </is>
-      </c>
-      <c r="E141">
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Filter Review</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="J141">
         <v>0</v>
       </c>
     </row>
